--- a/summary_stats/chuuchuu_summary_2025_11.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_11.xlsx
@@ -1454,25 +1454,25 @@
         <v>69</v>
       </c>
       <c r="N13" t="n">
-        <v>1018</v>
+        <v>1006</v>
       </c>
       <c r="O13" t="n">
-        <v>872</v>
+        <v>860</v>
       </c>
       <c r="P13" t="n">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="Q13" t="n">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="R13" t="n">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="S13" t="n">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="T13" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U13" t="n">
         <v>1537</v>
@@ -1849,25 +1849,25 @@
         <v>713</v>
       </c>
       <c r="N18" t="n">
-        <v>2697</v>
+        <v>2400</v>
       </c>
       <c r="O18" t="n">
-        <v>2382</v>
+        <v>2097</v>
       </c>
       <c r="P18" t="n">
-        <v>2237</v>
+        <v>1961</v>
       </c>
       <c r="Q18" t="n">
-        <v>1804</v>
+        <v>1557</v>
       </c>
       <c r="R18" t="n">
-        <v>1438</v>
+        <v>1221</v>
       </c>
       <c r="S18" t="n">
-        <v>720</v>
+        <v>567</v>
       </c>
       <c r="T18" t="n">
-        <v>187</v>
+        <v>145</v>
       </c>
       <c r="U18" t="n">
         <v>3923</v>
@@ -1928,25 +1928,25 @@
         <v>51</v>
       </c>
       <c r="N19" t="n">
-        <v>934</v>
+        <v>918</v>
       </c>
       <c r="O19" t="n">
-        <v>763</v>
+        <v>748</v>
       </c>
       <c r="P19" t="n">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="Q19" t="n">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="R19" t="n">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="S19" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="T19" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U19" t="n">
         <v>1530</v>
@@ -2007,25 +2007,25 @@
         <v>1610</v>
       </c>
       <c r="N20" t="n">
-        <v>9699</v>
+        <v>9033</v>
       </c>
       <c r="O20" t="n">
-        <v>8670</v>
+        <v>8045</v>
       </c>
       <c r="P20" t="n">
-        <v>8219</v>
+        <v>7605</v>
       </c>
       <c r="Q20" t="n">
-        <v>6697</v>
+        <v>6145</v>
       </c>
       <c r="R20" t="n">
-        <v>5262</v>
+        <v>4776</v>
       </c>
       <c r="S20" t="n">
-        <v>2766</v>
+        <v>2426</v>
       </c>
       <c r="T20" t="n">
-        <v>840</v>
+        <v>681</v>
       </c>
       <c r="U20" t="n">
         <v>13889</v>
@@ -2086,25 +2086,25 @@
         <v>223</v>
       </c>
       <c r="N21" t="n">
-        <v>2491</v>
+        <v>2392</v>
       </c>
       <c r="O21" t="n">
-        <v>2170</v>
+        <v>2073</v>
       </c>
       <c r="P21" t="n">
-        <v>2046</v>
+        <v>1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>1687</v>
+        <v>1601</v>
       </c>
       <c r="R21" t="n">
-        <v>1349</v>
+        <v>1267</v>
       </c>
       <c r="S21" t="n">
-        <v>669</v>
+        <v>613</v>
       </c>
       <c r="T21" t="n">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="U21" t="n">
         <v>3426</v>
@@ -2323,25 +2323,25 @@
         <v>6</v>
       </c>
       <c r="N24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>21</v>
@@ -2402,25 +2402,25 @@
         <v>41</v>
       </c>
       <c r="N25" t="n">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="O25" t="n">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="P25" t="n">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="Q25" t="n">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="R25" t="n">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="S25" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="T25" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="U25" t="n">
         <v>668</v>
@@ -2639,25 +2639,25 @@
         <v>13</v>
       </c>
       <c r="N28" t="n">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="O28" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="P28" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="Q28" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="R28" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="S28" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="T28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U28" t="n">
         <v>357</v>
@@ -3350,22 +3350,22 @@
         <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
@@ -3508,25 +3508,25 @@
         <v>484</v>
       </c>
       <c r="N39" t="n">
-        <v>901</v>
+        <v>818</v>
       </c>
       <c r="O39" t="n">
-        <v>887</v>
+        <v>804</v>
       </c>
       <c r="P39" t="n">
-        <v>881</v>
+        <v>798</v>
       </c>
       <c r="Q39" t="n">
-        <v>615</v>
+        <v>556</v>
       </c>
       <c r="R39" t="n">
-        <v>509</v>
+        <v>457</v>
       </c>
       <c r="S39" t="n">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="T39" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="U39" t="n">
         <v>3310</v>
@@ -3587,25 +3587,25 @@
         <v>22</v>
       </c>
       <c r="N40" t="n">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="O40" t="n">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="P40" t="n">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="Q40" t="n">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="R40" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="S40" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="T40" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U40" t="n">
         <v>424</v>
@@ -3666,10 +3666,10 @@
         <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O41" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P41" t="n">
         <v>23</v>
@@ -4614,22 +4614,22 @@
         <v>4323</v>
       </c>
       <c r="N53" t="n">
-        <v>6132</v>
+        <v>5900</v>
       </c>
       <c r="O53" t="n">
-        <v>3568</v>
+        <v>3414</v>
       </c>
       <c r="P53" t="n">
-        <v>2819</v>
+        <v>2685</v>
       </c>
       <c r="Q53" t="n">
-        <v>1353</v>
+        <v>1274</v>
       </c>
       <c r="R53" t="n">
-        <v>632</v>
+        <v>591</v>
       </c>
       <c r="S53" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="T53" t="n">
         <v>2</v>
@@ -4693,19 +4693,19 @@
         <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O54" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P54" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q54" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R54" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -4851,22 +4851,22 @@
         <v>625</v>
       </c>
       <c r="N56" t="n">
-        <v>680</v>
+        <v>572</v>
       </c>
       <c r="O56" t="n">
-        <v>461</v>
+        <v>372</v>
       </c>
       <c r="P56" t="n">
-        <v>396</v>
+        <v>312</v>
       </c>
       <c r="Q56" t="n">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="R56" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
@@ -4930,19 +4930,19 @@
         <v>13</v>
       </c>
       <c r="N57" t="n">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="O57" t="n">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="P57" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="Q57" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="R57" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S57" t="n">
         <v>80</v>
@@ -5009,19 +5009,19 @@
         <v>7</v>
       </c>
       <c r="N58" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O58" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P58" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q58" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R58" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S58" t="n">
         <v>60</v>
@@ -5167,22 +5167,22 @@
         <v>312</v>
       </c>
       <c r="N60" t="n">
-        <v>620</v>
+        <v>549</v>
       </c>
       <c r="O60" t="n">
-        <v>261</v>
+        <v>215</v>
       </c>
       <c r="P60" t="n">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="Q60" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R60" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T60" t="n">
         <v>0</v>
@@ -5325,22 +5325,22 @@
         <v>4452</v>
       </c>
       <c r="N62" t="n">
-        <v>8193</v>
+        <v>7954</v>
       </c>
       <c r="O62" t="n">
-        <v>3888</v>
+        <v>3759</v>
       </c>
       <c r="P62" t="n">
-        <v>2871</v>
+        <v>2762</v>
       </c>
       <c r="Q62" t="n">
-        <v>1109</v>
+        <v>1061</v>
       </c>
       <c r="R62" t="n">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="S62" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="T62" t="n">
         <v>5</v>
@@ -5404,22 +5404,22 @@
         <v>1206</v>
       </c>
       <c r="N63" t="n">
-        <v>4363</v>
+        <v>4252</v>
       </c>
       <c r="O63" t="n">
-        <v>1769</v>
+        <v>1706</v>
       </c>
       <c r="P63" t="n">
-        <v>1163</v>
+        <v>1110</v>
       </c>
       <c r="Q63" t="n">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="R63" t="n">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T63" t="n">
         <v>0</v>
@@ -6036,7 +6036,7 @@
         <v>18</v>
       </c>
       <c r="N71" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O71" t="n">
         <v>137</v>
@@ -6589,22 +6589,22 @@
         <v>90</v>
       </c>
       <c r="N78" t="n">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="O78" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="P78" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q78" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="R78" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S78" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="T78" t="n">
         <v>2</v>
@@ -6747,25 +6747,25 @@
         <v>25</v>
       </c>
       <c r="N80" t="n">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="O80" t="n">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="P80" t="n">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="Q80" t="n">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="R80" t="n">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="S80" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="T80" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U80" t="n">
         <v>1020</v>
@@ -6826,22 +6826,22 @@
         <v>8</v>
       </c>
       <c r="N81" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="O81" t="n">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="P81" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Q81" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="R81" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S81" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T81" t="n">
         <v>23</v>
@@ -7063,22 +7063,22 @@
         <v>23</v>
       </c>
       <c r="N84" t="n">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="O84" t="n">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="P84" t="n">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="Q84" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="R84" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S84" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="T84" t="n">
         <v>44</v>
@@ -7379,19 +7379,19 @@
         <v>2</v>
       </c>
       <c r="N88" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O88" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P88" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q88" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R88" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S88" t="n">
         <v>3</v>
@@ -7853,10 +7853,10 @@
         <v>37</v>
       </c>
       <c r="N94" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O94" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P94" t="n">
         <v>255</v>
@@ -8406,22 +8406,22 @@
         <v>206</v>
       </c>
       <c r="N101" t="n">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="O101" t="n">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="P101" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="Q101" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="R101" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="S101" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="T101" t="n">
         <v>7</v>
@@ -9670,19 +9670,19 @@
         <v>13</v>
       </c>
       <c r="N117" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="O117" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="P117" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="Q117" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="R117" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -9828,25 +9828,25 @@
         <v>445</v>
       </c>
       <c r="N119" t="n">
-        <v>5062</v>
+        <v>4999</v>
       </c>
       <c r="O119" t="n">
-        <v>3026</v>
+        <v>2973</v>
       </c>
       <c r="P119" t="n">
-        <v>2398</v>
+        <v>2349</v>
       </c>
       <c r="Q119" t="n">
-        <v>1120</v>
+        <v>1084</v>
       </c>
       <c r="R119" t="n">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="S119" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="T119" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U119" t="n">
         <v>25493</v>
@@ -10065,22 +10065,22 @@
         <v>7</v>
       </c>
       <c r="N122" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O122" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P122" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q122" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R122" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S122" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T122" t="n">
         <v>2</v>
@@ -10144,19 +10144,19 @@
         <v>87</v>
       </c>
       <c r="N123" t="n">
-        <v>2333</v>
+        <v>2326</v>
       </c>
       <c r="O123" t="n">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="P123" t="n">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="Q123" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="R123" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S123" t="n">
         <v>22</v>
@@ -10460,13 +10460,13 @@
         <v>41</v>
       </c>
       <c r="N127" t="n">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="O127" t="n">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="P127" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q127" t="n">
         <v>185</v>
@@ -10618,22 +10618,22 @@
         <v>272</v>
       </c>
       <c r="N129" t="n">
-        <v>3520</v>
+        <v>3493</v>
       </c>
       <c r="O129" t="n">
-        <v>1905</v>
+        <v>1885</v>
       </c>
       <c r="P129" t="n">
-        <v>1492</v>
+        <v>1474</v>
       </c>
       <c r="Q129" t="n">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="R129" t="n">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="S129" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="T129" t="n">
         <v>1</v>
@@ -10697,16 +10697,16 @@
         <v>82</v>
       </c>
       <c r="N130" t="n">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="O130" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P130" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="Q130" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R130" t="n">
         <v>48</v>
@@ -10855,7 +10855,7 @@
         <v>56</v>
       </c>
       <c r="N132" t="n">
-        <v>4200</v>
+        <v>4199</v>
       </c>
       <c r="O132" t="n">
         <v>1273</v>
@@ -11092,25 +11092,25 @@
         <v>36</v>
       </c>
       <c r="N135" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="O135" t="n">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="P135" t="n">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="Q135" t="n">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="R135" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="S135" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="T135" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="U135" t="n">
         <v>1581</v>
@@ -12119,25 +12119,25 @@
         <v>13</v>
       </c>
       <c r="N148" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O148" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P148" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q148" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R148" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S148" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T148" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U148" t="n">
         <v>23</v>
@@ -12198,25 +12198,25 @@
         <v>99</v>
       </c>
       <c r="N149" t="n">
-        <v>2954</v>
+        <v>2930</v>
       </c>
       <c r="O149" t="n">
-        <v>1821</v>
+        <v>1802</v>
       </c>
       <c r="P149" t="n">
-        <v>1821</v>
+        <v>1802</v>
       </c>
       <c r="Q149" t="n">
-        <v>1296</v>
+        <v>1278</v>
       </c>
       <c r="R149" t="n">
-        <v>963</v>
+        <v>948</v>
       </c>
       <c r="S149" t="n">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="T149" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="U149" t="n">
         <v>11424</v>
@@ -12277,16 +12277,16 @@
         <v>5</v>
       </c>
       <c r="N150" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="O150" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P150" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q150" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R150" t="n">
         <v>160</v>
@@ -12435,25 +12435,25 @@
         <v>4536</v>
       </c>
       <c r="N152" t="n">
-        <v>24230</v>
+        <v>23889</v>
       </c>
       <c r="O152" t="n">
-        <v>11323</v>
+        <v>11075</v>
       </c>
       <c r="P152" t="n">
-        <v>11298</v>
+        <v>11050</v>
       </c>
       <c r="Q152" t="n">
-        <v>7276</v>
+        <v>7095</v>
       </c>
       <c r="R152" t="n">
-        <v>5168</v>
+        <v>5018</v>
       </c>
       <c r="S152" t="n">
-        <v>2228</v>
+        <v>2137</v>
       </c>
       <c r="T152" t="n">
-        <v>467</v>
+        <v>434</v>
       </c>
       <c r="U152" t="n">
         <v>149986</v>
@@ -12514,25 +12514,25 @@
         <v>455</v>
       </c>
       <c r="N153" t="n">
-        <v>2686</v>
+        <v>2668</v>
       </c>
       <c r="O153" t="n">
-        <v>1053</v>
+        <v>1040</v>
       </c>
       <c r="P153" t="n">
-        <v>1051</v>
+        <v>1038</v>
       </c>
       <c r="Q153" t="n">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="R153" t="n">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="S153" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="T153" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="U153" t="n">
         <v>20891</v>
@@ -12751,19 +12751,19 @@
         <v>90</v>
       </c>
       <c r="N156" t="n">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="O156" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P156" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q156" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R156" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S156" t="n">
         <v>9</v>
@@ -13612,22 +13612,22 @@
         <v>33</v>
       </c>
       <c r="N167" t="n">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="O167" t="n">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="P167" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="Q167" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="R167" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S167" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="T167" t="n">
         <v>11</v>
@@ -13849,25 +13849,25 @@
         <v>2</v>
       </c>
       <c r="N170" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O170" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P170" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q170" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R170" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S170" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T170" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U170" t="n">
         <v>40</v>
@@ -14086,16 +14086,16 @@
         <v>7</v>
       </c>
       <c r="N173" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O173" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P173" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q173" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R173" t="n">
         <v>105</v>
@@ -14165,25 +14165,25 @@
         <v>8</v>
       </c>
       <c r="N174" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O174" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="P174" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="Q174" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="R174" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="S174" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T174" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U174" t="n">
         <v>236</v>
@@ -14244,25 +14244,25 @@
         <v>64</v>
       </c>
       <c r="N175" t="n">
-        <v>3326</v>
+        <v>3288</v>
       </c>
       <c r="O175" t="n">
-        <v>2745</v>
+        <v>2711</v>
       </c>
       <c r="P175" t="n">
-        <v>2488</v>
+        <v>2455</v>
       </c>
       <c r="Q175" t="n">
-        <v>1799</v>
+        <v>1767</v>
       </c>
       <c r="R175" t="n">
-        <v>1339</v>
+        <v>1308</v>
       </c>
       <c r="S175" t="n">
-        <v>715</v>
+        <v>690</v>
       </c>
       <c r="T175" t="n">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="U175" t="n">
         <v>6557</v>
@@ -14323,25 +14323,25 @@
         <v>90</v>
       </c>
       <c r="N176" t="n">
-        <v>1284</v>
+        <v>1271</v>
       </c>
       <c r="O176" t="n">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="P176" t="n">
-        <v>929</v>
+        <v>916</v>
       </c>
       <c r="Q176" t="n">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="R176" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="S176" t="n">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="T176" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="U176" t="n">
         <v>3200</v>
@@ -14481,13 +14481,13 @@
         <v>5</v>
       </c>
       <c r="N178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q178" t="n">
         <v>1</v>
@@ -14639,13 +14639,13 @@
         <v>132</v>
       </c>
       <c r="N180" t="n">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="O180" t="n">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="P180" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Q180" t="n">
         <v>101</v>
@@ -15034,25 +15034,25 @@
         <v>8008</v>
       </c>
       <c r="N185" t="n">
-        <v>48188</v>
+        <v>47656</v>
       </c>
       <c r="O185" t="n">
-        <v>27395</v>
+        <v>27011</v>
       </c>
       <c r="P185" t="n">
-        <v>21528</v>
+        <v>21188</v>
       </c>
       <c r="Q185" t="n">
-        <v>10546</v>
+        <v>10308</v>
       </c>
       <c r="R185" t="n">
-        <v>5951</v>
+        <v>5780</v>
       </c>
       <c r="S185" t="n">
-        <v>1801</v>
+        <v>1725</v>
       </c>
       <c r="T185" t="n">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="U185" t="n">
         <v>217218</v>
@@ -15113,22 +15113,22 @@
         <v>296</v>
       </c>
       <c r="N186" t="n">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="O186" t="n">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="P186" t="n">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="Q186" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="R186" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="S186" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T186" t="n">
         <v>1</v>
@@ -16764,22 +16764,22 @@
         <v>9</v>
       </c>
       <c r="N207" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="O207" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="P207" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="Q207" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="R207" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="S207" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T207" t="n">
         <v>4</v>
@@ -17463,25 +17463,25 @@
         <v>13</v>
       </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="U5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
         <v>23</v>
@@ -18051,7 +18051,7 @@
         <v>56</v>
       </c>
       <c r="O12" t="n">
-        <v>4200</v>
+        <v>4199</v>
       </c>
       <c r="P12" t="n">
         <v>1273</v>
@@ -18303,25 +18303,25 @@
         <v>36</v>
       </c>
       <c r="O15" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="P15" t="n">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="Q15" t="n">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="R15" t="n">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="S15" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="T15" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="U15" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="V15" t="n">
         <v>1581</v>
@@ -19227,25 +19227,25 @@
         <v>99</v>
       </c>
       <c r="O26" t="n">
-        <v>2954</v>
+        <v>2930</v>
       </c>
       <c r="P26" t="n">
-        <v>1821</v>
+        <v>1802</v>
       </c>
       <c r="Q26" t="n">
-        <v>1821</v>
+        <v>1802</v>
       </c>
       <c r="R26" t="n">
-        <v>1296</v>
+        <v>1278</v>
       </c>
       <c r="S26" t="n">
-        <v>963</v>
+        <v>948</v>
       </c>
       <c r="T26" t="n">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="U26" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="V26" t="n">
         <v>11424</v>
@@ -19311,16 +19311,16 @@
         <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P27" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q27" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="R27" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S27" t="n">
         <v>157</v>
@@ -19479,25 +19479,25 @@
         <v>4536</v>
       </c>
       <c r="O29" t="n">
-        <v>24230</v>
+        <v>23889</v>
       </c>
       <c r="P29" t="n">
-        <v>11323</v>
+        <v>11075</v>
       </c>
       <c r="Q29" t="n">
-        <v>11298</v>
+        <v>11050</v>
       </c>
       <c r="R29" t="n">
-        <v>7276</v>
+        <v>7095</v>
       </c>
       <c r="S29" t="n">
-        <v>5168</v>
+        <v>5018</v>
       </c>
       <c r="T29" t="n">
-        <v>2228</v>
+        <v>2137</v>
       </c>
       <c r="U29" t="n">
-        <v>467</v>
+        <v>434</v>
       </c>
       <c r="V29" t="n">
         <v>149986</v>
@@ -19563,25 +19563,25 @@
         <v>406</v>
       </c>
       <c r="O30" t="n">
-        <v>2554</v>
+        <v>2536</v>
       </c>
       <c r="P30" t="n">
-        <v>1021</v>
+        <v>1008</v>
       </c>
       <c r="Q30" t="n">
-        <v>1019</v>
+        <v>1006</v>
       </c>
       <c r="R30" t="n">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="S30" t="n">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="T30" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="U30" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="V30" t="n">
         <v>19557</v>
@@ -19731,19 +19731,19 @@
         <v>90</v>
       </c>
       <c r="O32" t="n">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="P32" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q32" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R32" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S32" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T32" t="n">
         <v>9</v>
@@ -20269,22 +20269,22 @@
         <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U2" t="n">
         <v>8</v>
@@ -21361,25 +21361,25 @@
         <v>712</v>
       </c>
       <c r="O15" t="n">
-        <v>2682</v>
+        <v>2385</v>
       </c>
       <c r="P15" t="n">
-        <v>2369</v>
+        <v>2084</v>
       </c>
       <c r="Q15" t="n">
-        <v>2224</v>
+        <v>1948</v>
       </c>
       <c r="R15" t="n">
-        <v>1794</v>
+        <v>1547</v>
       </c>
       <c r="S15" t="n">
-        <v>1435</v>
+        <v>1218</v>
       </c>
       <c r="T15" t="n">
-        <v>719</v>
+        <v>566</v>
       </c>
       <c r="U15" t="n">
-        <v>187</v>
+        <v>145</v>
       </c>
       <c r="V15" t="n">
         <v>3904</v>
@@ -21445,22 +21445,22 @@
         <v>7</v>
       </c>
       <c r="O16" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="P16" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Q16" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="R16" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="S16" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="T16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="U16" t="n">
         <v>6</v>
@@ -21529,25 +21529,25 @@
         <v>1610</v>
       </c>
       <c r="O17" t="n">
-        <v>9699</v>
+        <v>9033</v>
       </c>
       <c r="P17" t="n">
-        <v>8670</v>
+        <v>8045</v>
       </c>
       <c r="Q17" t="n">
-        <v>8219</v>
+        <v>7605</v>
       </c>
       <c r="R17" t="n">
-        <v>6697</v>
+        <v>6145</v>
       </c>
       <c r="S17" t="n">
-        <v>5262</v>
+        <v>4776</v>
       </c>
       <c r="T17" t="n">
-        <v>2766</v>
+        <v>2426</v>
       </c>
       <c r="U17" t="n">
-        <v>840</v>
+        <v>681</v>
       </c>
       <c r="V17" t="n">
         <v>13889</v>
@@ -21781,19 +21781,19 @@
         <v>18</v>
       </c>
       <c r="O20" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P20" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q20" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R20" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S20" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T20" t="n">
         <v>23</v>
@@ -22453,25 +22453,25 @@
         <v>42</v>
       </c>
       <c r="O28" t="n">
-        <v>583</v>
+        <v>565</v>
       </c>
       <c r="P28" t="n">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="Q28" t="n">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="R28" t="n">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="S28" t="n">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="T28" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="U28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="V28" t="n">
         <v>825</v>
@@ -22537,22 +22537,22 @@
         <v>10</v>
       </c>
       <c r="O29" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="P29" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q29" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="R29" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="S29" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="T29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="U29" t="n">
         <v>3</v>
@@ -22705,25 +22705,25 @@
         <v>9</v>
       </c>
       <c r="O31" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="P31" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q31" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="R31" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="S31" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V31" t="n">
         <v>162</v>
@@ -22789,25 +22789,25 @@
         <v>61</v>
       </c>
       <c r="O32" t="n">
-        <v>526</v>
+        <v>494</v>
       </c>
       <c r="P32" t="n">
-        <v>484</v>
+        <v>453</v>
       </c>
       <c r="Q32" t="n">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="R32" t="n">
-        <v>414</v>
+        <v>385</v>
       </c>
       <c r="S32" t="n">
-        <v>359</v>
+        <v>331</v>
       </c>
       <c r="T32" t="n">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="U32" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="V32" t="n">
         <v>659</v>
@@ -23125,25 +23125,25 @@
         <v>2</v>
       </c>
       <c r="O36" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P36" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Q36" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R36" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S36" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="T36" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V36" t="n">
         <v>56</v>
@@ -23209,25 +23209,25 @@
         <v>7</v>
       </c>
       <c r="O37" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="P37" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="Q37" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="R37" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="S37" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="T37" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V37" t="n">
         <v>227</v>
@@ -23377,25 +23377,25 @@
         <v>11</v>
       </c>
       <c r="O39" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P39" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="Q39" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="R39" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="S39" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T39" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="U39" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="V39" t="n">
         <v>64</v>
@@ -23545,22 +23545,22 @@
         <v>13</v>
       </c>
       <c r="O41" t="n">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="P41" t="n">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="Q41" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="R41" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="S41" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="T41" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="U41" t="n">
         <v>24</v>
@@ -23629,25 +23629,25 @@
         <v>90</v>
       </c>
       <c r="O42" t="n">
-        <v>850</v>
+        <v>806</v>
       </c>
       <c r="P42" t="n">
-        <v>751</v>
+        <v>707</v>
       </c>
       <c r="Q42" t="n">
-        <v>713</v>
+        <v>671</v>
       </c>
       <c r="R42" t="n">
-        <v>610</v>
+        <v>569</v>
       </c>
       <c r="S42" t="n">
-        <v>491</v>
+        <v>452</v>
       </c>
       <c r="T42" t="n">
-        <v>268</v>
+        <v>239</v>
       </c>
       <c r="U42" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="V42" t="n">
         <v>1135</v>
@@ -23797,22 +23797,22 @@
         <v>11</v>
       </c>
       <c r="O44" t="n">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P44" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q44" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="R44" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S44" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="T44" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="U44" t="n">
         <v>4</v>
@@ -23881,13 +23881,13 @@
         <v>13</v>
       </c>
       <c r="O45" t="n">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="P45" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Q45" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="R45" t="n">
         <v>148</v>
@@ -24301,25 +24301,25 @@
         <v>6</v>
       </c>
       <c r="O50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V50" t="n">
         <v>21</v>
@@ -24385,25 +24385,25 @@
         <v>41</v>
       </c>
       <c r="O51" t="n">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="P51" t="n">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="Q51" t="n">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="R51" t="n">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="S51" t="n">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="T51" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="U51" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V51" t="n">
         <v>668</v>
@@ -24889,19 +24889,19 @@
         <v>20</v>
       </c>
       <c r="O57" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="P57" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q57" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="R57" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="S57" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="T57" t="n">
         <v>40</v>
@@ -25519,19 +25519,19 @@
         <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="P3" t="n">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="Q3" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="R3" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="S3" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -25603,19 +25603,19 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
         <v>9</v>
@@ -25771,22 +25771,22 @@
         <v>4323</v>
       </c>
       <c r="O6" t="n">
-        <v>6132</v>
+        <v>5900</v>
       </c>
       <c r="P6" t="n">
-        <v>3568</v>
+        <v>3414</v>
       </c>
       <c r="Q6" t="n">
-        <v>2819</v>
+        <v>2685</v>
       </c>
       <c r="R6" t="n">
-        <v>1353</v>
+        <v>1274</v>
       </c>
       <c r="S6" t="n">
-        <v>632</v>
+        <v>591</v>
       </c>
       <c r="T6" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="U6" t="n">
         <v>2</v>
@@ -25939,22 +25939,22 @@
         <v>625</v>
       </c>
       <c r="O8" t="n">
-        <v>680</v>
+        <v>572</v>
       </c>
       <c r="P8" t="n">
-        <v>461</v>
+        <v>372</v>
       </c>
       <c r="Q8" t="n">
-        <v>396</v>
+        <v>312</v>
       </c>
       <c r="R8" t="n">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="S8" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="T8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -26107,22 +26107,22 @@
         <v>312</v>
       </c>
       <c r="O10" t="n">
-        <v>620</v>
+        <v>549</v>
       </c>
       <c r="P10" t="n">
-        <v>261</v>
+        <v>215</v>
       </c>
       <c r="Q10" t="n">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="R10" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="S10" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="T10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -26275,22 +26275,22 @@
         <v>4452</v>
       </c>
       <c r="O12" t="n">
-        <v>8193</v>
+        <v>7954</v>
       </c>
       <c r="P12" t="n">
-        <v>3888</v>
+        <v>3759</v>
       </c>
       <c r="Q12" t="n">
-        <v>2871</v>
+        <v>2762</v>
       </c>
       <c r="R12" t="n">
-        <v>1109</v>
+        <v>1061</v>
       </c>
       <c r="S12" t="n">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="T12" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
@@ -26359,22 +26359,22 @@
         <v>1206</v>
       </c>
       <c r="O13" t="n">
-        <v>4363</v>
+        <v>4252</v>
       </c>
       <c r="P13" t="n">
-        <v>1769</v>
+        <v>1706</v>
       </c>
       <c r="Q13" t="n">
-        <v>1163</v>
+        <v>1110</v>
       </c>
       <c r="R13" t="n">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="S13" t="n">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="T13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -26611,19 +26611,19 @@
         <v>7</v>
       </c>
       <c r="O16" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P16" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q16" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R16" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="S16" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T16" t="n">
         <v>60</v>
@@ -30181,7 +30181,7 @@
         <v>18</v>
       </c>
       <c r="O42" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="P42" t="n">
         <v>137</v>
@@ -30601,22 +30601,22 @@
         <v>90</v>
       </c>
       <c r="O47" t="n">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="P47" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="Q47" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="R47" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="S47" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T47" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="U47" t="n">
         <v>2</v>
@@ -30769,25 +30769,25 @@
         <v>25</v>
       </c>
       <c r="O49" t="n">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="P49" t="n">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="Q49" t="n">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="R49" t="n">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="S49" t="n">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="T49" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="U49" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V49" t="n">
         <v>1020</v>
@@ -30853,22 +30853,22 @@
         <v>5</v>
       </c>
       <c r="O50" t="n">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P50" t="n">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Q50" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="R50" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="S50" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T50" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U50" t="n">
         <v>22</v>
@@ -32239,10 +32239,10 @@
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q8" t="n">
         <v>37</v>
@@ -32491,22 +32491,22 @@
         <v>206</v>
       </c>
       <c r="O11" t="n">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="P11" t="n">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="Q11" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="R11" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="S11" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="T11" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="U11" t="n">
         <v>7</v>
@@ -35053,22 +35053,22 @@
         <v>7</v>
       </c>
       <c r="O2" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P2" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="U2" t="n">
         <v>2</v>
@@ -35137,19 +35137,19 @@
         <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="P3" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="Q3" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="R3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -35389,25 +35389,25 @@
         <v>445</v>
       </c>
       <c r="O6" t="n">
-        <v>5062</v>
+        <v>4999</v>
       </c>
       <c r="P6" t="n">
-        <v>3026</v>
+        <v>2973</v>
       </c>
       <c r="Q6" t="n">
-        <v>2398</v>
+        <v>2349</v>
       </c>
       <c r="R6" t="n">
-        <v>1120</v>
+        <v>1084</v>
       </c>
       <c r="S6" t="n">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="T6" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="U6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V6" t="n">
         <v>25493</v>
@@ -35641,19 +35641,19 @@
         <v>87</v>
       </c>
       <c r="O9" t="n">
-        <v>2333</v>
+        <v>2326</v>
       </c>
       <c r="P9" t="n">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="Q9" t="n">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="R9" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="S9" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="T9" t="n">
         <v>22</v>
@@ -35809,13 +35809,13 @@
         <v>41</v>
       </c>
       <c r="O11" t="n">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="P11" t="n">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Q11" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="R11" t="n">
         <v>185</v>
@@ -35977,22 +35977,22 @@
         <v>272</v>
       </c>
       <c r="O13" t="n">
-        <v>3520</v>
+        <v>3493</v>
       </c>
       <c r="P13" t="n">
-        <v>1905</v>
+        <v>1885</v>
       </c>
       <c r="Q13" t="n">
-        <v>1492</v>
+        <v>1474</v>
       </c>
       <c r="R13" t="n">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="S13" t="n">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="T13" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="U13" t="n">
         <v>1</v>
@@ -36061,16 +36061,16 @@
         <v>81</v>
       </c>
       <c r="O14" t="n">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="P14" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Q14" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="R14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="S14" t="n">
         <v>46</v>
@@ -36775,22 +36775,22 @@
         <v>10</v>
       </c>
       <c r="O4" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P4" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q4" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R4" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="T4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U4" t="n">
         <v>8</v>
@@ -37783,16 +37783,16 @@
         <v>21</v>
       </c>
       <c r="O16" t="n">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="P16" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q16" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="R16" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="S16" t="n">
         <v>54</v>
@@ -38035,25 +38035,25 @@
         <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V19" t="n">
         <v>40</v>
@@ -38287,16 +38287,16 @@
         <v>7</v>
       </c>
       <c r="O22" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P22" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q22" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R22" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S22" t="n">
         <v>105</v>
@@ -38371,25 +38371,25 @@
         <v>8</v>
       </c>
       <c r="O23" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="P23" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="Q23" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="R23" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="S23" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T23" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="U23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V23" t="n">
         <v>236</v>
@@ -38455,25 +38455,25 @@
         <v>64</v>
       </c>
       <c r="O24" t="n">
-        <v>3326</v>
+        <v>3288</v>
       </c>
       <c r="P24" t="n">
-        <v>2745</v>
+        <v>2711</v>
       </c>
       <c r="Q24" t="n">
-        <v>2488</v>
+        <v>2455</v>
       </c>
       <c r="R24" t="n">
-        <v>1799</v>
+        <v>1767</v>
       </c>
       <c r="S24" t="n">
-        <v>1339</v>
+        <v>1308</v>
       </c>
       <c r="T24" t="n">
-        <v>715</v>
+        <v>690</v>
       </c>
       <c r="U24" t="n">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="V24" t="n">
         <v>6557</v>
@@ -38539,25 +38539,25 @@
         <v>90</v>
       </c>
       <c r="O25" t="n">
-        <v>1284</v>
+        <v>1271</v>
       </c>
       <c r="P25" t="n">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="Q25" t="n">
-        <v>929</v>
+        <v>916</v>
       </c>
       <c r="R25" t="n">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="S25" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="T25" t="n">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="U25" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="V25" t="n">
         <v>3200</v>
@@ -38707,13 +38707,13 @@
         <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -38791,13 +38791,13 @@
         <v>132</v>
       </c>
       <c r="O28" t="n">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="P28" t="n">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="Q28" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="R28" t="n">
         <v>101</v>
@@ -39043,25 +39043,25 @@
         <v>8008</v>
       </c>
       <c r="O31" t="n">
-        <v>48188</v>
+        <v>47656</v>
       </c>
       <c r="P31" t="n">
-        <v>27395</v>
+        <v>27011</v>
       </c>
       <c r="Q31" t="n">
-        <v>21528</v>
+        <v>21188</v>
       </c>
       <c r="R31" t="n">
-        <v>10546</v>
+        <v>10308</v>
       </c>
       <c r="S31" t="n">
-        <v>5951</v>
+        <v>5780</v>
       </c>
       <c r="T31" t="n">
-        <v>1801</v>
+        <v>1725</v>
       </c>
       <c r="U31" t="n">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="V31" t="n">
         <v>217218</v>
@@ -39127,22 +39127,22 @@
         <v>296</v>
       </c>
       <c r="O32" t="n">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="P32" t="n">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="Q32" t="n">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="R32" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="S32" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="T32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U32" t="n">
         <v>1</v>

--- a/summary_stats/chuuchuu_summary_2025_11.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_11.xlsx
@@ -16752,7 +16752,7 @@
         </is>
       </c>
       <c r="J207" t="n">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="K207" t="n">
         <v>0</v>
@@ -16764,28 +16764,28 @@
         <v>9</v>
       </c>
       <c r="N207" t="n">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="O207" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="P207" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="Q207" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="R207" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="S207" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T207" t="n">
         <v>4</v>
       </c>
       <c r="U207" t="n">
-        <v>302</v>
+        <v>314</v>
       </c>
     </row>
     <row r="208">
